--- a/vgjewellry/public/sample/quotation_template_new.xlsx
+++ b/vgjewellry/public/sample/quotation_template_new.xlsx
@@ -230,9 +230,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>286560</xdr:colOff>
+      <xdr:colOff>286200</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>162000</xdr:rowOff>
+      <xdr:rowOff>161640</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -246,7 +246,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="1626840" y="450720"/>
-          <a:ext cx="286560" cy="162000"/>
+          <a:ext cx="286200" cy="161640"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -268,9 +268,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>286560</xdr:colOff>
+      <xdr:colOff>286200</xdr:colOff>
       <xdr:row>3</xdr:row>
-      <xdr:rowOff>162000</xdr:rowOff>
+      <xdr:rowOff>161640</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -284,7 +284,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="1626840" y="774720"/>
-          <a:ext cx="286560" cy="162000"/>
+          <a:ext cx="286200" cy="161640"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -411,7 +411,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:V1048576"/>
+  <dimension ref="A1:V4"/>
   <sheetFormatPr defaultColWidth="11.54296875" defaultRowHeight="12.75" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -630,18 +630,26 @@
         <v>28888</v>
       </c>
     </row>
-    <row r="1048573" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
-  <dataValidations count="2">
+  <dataValidations count="5">
     <dataValidation allowBlank="false" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="F1:F998" type="list">
       <formula1>"Gold 14KT,Gold 18KT,Platinum"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="false" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D1:D998" type="list">
       <formula1>"Bangles,Button,Cufflink,Pendant,Polki,Ring,Set,Tops,Chain,Bali,Tanmania,Mangalsutra"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="false" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="J1" type="none">
+      <formula1>0</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="false" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="J2:J3 J5:J1004" type="list">
+      <formula1>"Round,Radiant,Oval,Pear,Emerald,Rose Cut,Heart,Princess,Baguette,Cushion,Marquise"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="false" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="J4" type="list">
+      <formula1>"Round,Radiant,Oval,Pear,Emerald,Rose Cut,Heart,Princess,Baguette,Cushion,Marquise"</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>

--- a/vgjewellry/public/sample/quotation_template_new.xlsx
+++ b/vgjewellry/public/sample/quotation_template_new.xlsx
@@ -230,9 +230,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>286200</xdr:colOff>
+      <xdr:colOff>285840</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>161640</xdr:rowOff>
+      <xdr:rowOff>161280</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -246,7 +246,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="1626840" y="450720"/>
-          <a:ext cx="286200" cy="161640"/>
+          <a:ext cx="285840" cy="161280"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -268,9 +268,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>286200</xdr:colOff>
+      <xdr:colOff>285840</xdr:colOff>
       <xdr:row>3</xdr:row>
-      <xdr:rowOff>161640</xdr:rowOff>
+      <xdr:rowOff>161280</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -284,7 +284,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="1626840" y="774720"/>
-          <a:ext cx="286200" cy="161640"/>
+          <a:ext cx="285840" cy="161280"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -631,12 +631,12 @@
       </c>
     </row>
   </sheetData>
-  <dataValidations count="5">
+  <dataValidations count="6">
     <dataValidation allowBlank="false" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="F1:F998" type="list">
       <formula1>"Gold 14KT,Gold 18KT,Platinum"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="false" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D1:D998" type="list">
+    <dataValidation allowBlank="false" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D1:D3 D5:D998" type="list">
       <formula1>"Bangles,Button,Cufflink,Pendant,Polki,Ring,Set,Tops,Chain,Bali,Tanmania,Mangalsutra"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -652,6 +652,10 @@
       <formula1>"Round,Radiant,Oval,Pear,Emerald,Rose Cut,Heart,Princess,Baguette,Cushion,Marquise"</formula1>
       <formula2>0</formula2>
     </dataValidation>
+    <dataValidation allowBlank="false" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D4" type="list">
+      <formula1>"Bangles,Bracelet,Button,Cufflink,Pendant,Polki,Ring,Set,Tops,Chain,Bali,Tanmania,Mangalsutra"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
   </dataValidations>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>

--- a/vgjewellry/public/sample/quotation_template_new.xlsx
+++ b/vgjewellry/public/sample/quotation_template_new.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="32">
   <si>
     <t xml:space="preserve">Vendor Code</t>
   </si>
@@ -106,7 +106,16 @@
     <t xml:space="preserve">Round</t>
   </si>
   <si>
+    <t xml:space="preserve">1 1/2 – 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+000 – 00</t>
+  </si>
+  <si>
     <t xml:space="preserve">R1002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 1/2 - 2</t>
   </si>
 </sst>
 </file>
@@ -116,7 +125,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -151,6 +160,12 @@
       <family val="1"/>
       <charset val="1"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -194,7 +209,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -204,6 +219,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -230,9 +249,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>285840</xdr:colOff>
+      <xdr:colOff>285480</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>161280</xdr:rowOff>
+      <xdr:rowOff>160920</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -246,7 +265,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="1626840" y="450720"/>
-          <a:ext cx="285840" cy="161280"/>
+          <a:ext cx="285480" cy="160920"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -268,9 +287,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>285840</xdr:colOff>
+      <xdr:colOff>285480</xdr:colOff>
       <xdr:row>3</xdr:row>
-      <xdr:rowOff>161280</xdr:rowOff>
+      <xdr:rowOff>160920</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -284,7 +303,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="1626840" y="774720"/>
-          <a:ext cx="285840" cy="161280"/>
+          <a:ext cx="285480" cy="160920"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -413,6 +432,9 @@
   </sheetPr>
   <dimension ref="A1:V4"/>
   <sheetFormatPr defaultColWidth="11.54296875" defaultRowHeight="12.75" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="14.2"/>
+  </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
@@ -511,8 +533,8 @@
       <c r="J2" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="K2" s="2" t="n">
-        <v>1.2</v>
+      <c r="K2" s="3" t="s">
+        <v>28</v>
       </c>
       <c r="L2" s="2" t="n">
         <v>12</v>
@@ -552,8 +574,8 @@
       <c r="J3" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="K3" s="2" t="n">
-        <v>0.9</v>
+      <c r="K3" s="3" t="s">
+        <v>29</v>
       </c>
       <c r="L3" s="2" t="n">
         <v>20</v>
@@ -576,7 +598,7 @@
         <v>24</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>26</v>
@@ -593,8 +615,8 @@
       <c r="J4" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="K4" s="2" t="n">
-        <v>1.3</v>
+      <c r="K4" s="2" t="s">
+        <v>31</v>
       </c>
       <c r="L4" s="2" t="n">
         <v>49</v>

--- a/vgjewellry/public/sample/quotation_template_new.xlsx
+++ b/vgjewellry/public/sample/quotation_template_new.xlsx
@@ -165,6 +165,7 @@
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -209,8 +210,12 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -249,9 +254,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>285480</xdr:colOff>
+      <xdr:colOff>285120</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>160920</xdr:rowOff>
+      <xdr:rowOff>160560</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -265,7 +270,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="1626840" y="450720"/>
-          <a:ext cx="285480" cy="160920"/>
+          <a:ext cx="285120" cy="160560"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -287,9 +292,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>285480</xdr:colOff>
+      <xdr:colOff>285120</xdr:colOff>
       <xdr:row>3</xdr:row>
-      <xdr:rowOff>160920</xdr:rowOff>
+      <xdr:rowOff>160560</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -303,7 +308,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="1626840" y="774720"/>
-          <a:ext cx="285480" cy="160920"/>
+          <a:ext cx="285120" cy="160560"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -433,249 +438,245 @@
   <dimension ref="A1:V4"/>
   <sheetFormatPr defaultColWidth="11.54296875" defaultRowHeight="12.75" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="14.2"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="14.2"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="P1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="Q1" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="R1" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="S1" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="T1" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="U1" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="V1" s="2" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2" t="s">
+      <c r="C2" s="3"/>
+      <c r="D2" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G2" s="2" t="n">
+      <c r="G2" s="3" t="n">
         <v>12.5</v>
       </c>
-      <c r="H2" s="2" t="n">
+      <c r="H2" s="3" t="n">
         <v>11.95</v>
       </c>
-      <c r="I2" s="2" t="n">
+      <c r="I2" s="3" t="n">
         <v>85000</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="J2" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="K2" s="3" t="s">
+      <c r="K2" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="L2" s="2" t="n">
+      <c r="L2" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="M2" s="2" t="n">
+      <c r="M2" s="3" t="n">
         <v>0.18</v>
       </c>
-      <c r="N2" s="2" t="n">
+      <c r="N2" s="3" t="n">
         <v>55000</v>
       </c>
-      <c r="O2" s="2" t="n">
+      <c r="O2" s="3" t="n">
         <v>9900</v>
       </c>
-      <c r="P2" s="2" t="n">
+      <c r="P2" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="Q2" s="2" t="n">
+      <c r="Q2" s="3" t="n">
         <v>1.25</v>
       </c>
-      <c r="R2" s="2" t="n">
+      <c r="R2" s="3" t="n">
         <v>2737</v>
       </c>
-      <c r="S2" s="2" t="n">
+      <c r="S2" s="3" t="n">
         <v>3500</v>
       </c>
-      <c r="T2" s="2" t="n">
+      <c r="T2" s="3" t="n">
         <v>3555</v>
       </c>
-      <c r="U2" s="2" t="n">
+      <c r="U2" s="3" t="n">
         <v>2500</v>
       </c>
-      <c r="V2" s="2" t="n">
+      <c r="V2" s="3" t="n">
         <v>105900</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J3" s="2" t="s">
+      <c r="J3" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="K3" s="3" t="s">
+      <c r="K3" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="L3" s="2" t="n">
+      <c r="L3" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="M3" s="2" t="n">
+      <c r="M3" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="N3" s="2" t="n">
+      <c r="N3" s="3" t="n">
         <v>50000</v>
       </c>
-      <c r="O3" s="2" t="n">
+      <c r="O3" s="3" t="n">
         <v>5000</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2"/>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2" t="s">
+      <c r="A4" s="3"/>
+      <c r="B4" s="3"/>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F4" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G4" s="2" t="n">
+      <c r="G4" s="3" t="n">
         <v>14.5</v>
       </c>
-      <c r="H4" s="2" t="n">
+      <c r="H4" s="3" t="n">
         <v>10.8</v>
       </c>
-      <c r="I4" s="2" t="n">
+      <c r="I4" s="3" t="n">
         <v>85000</v>
       </c>
-      <c r="J4" s="2" t="s">
+      <c r="J4" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="K4" s="2" t="s">
+      <c r="K4" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="L4" s="2" t="n">
+      <c r="L4" s="3" t="n">
         <v>49</v>
       </c>
-      <c r="M4" s="2" t="n">
+      <c r="M4" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="N4" s="2" t="n">
+      <c r="N4" s="3" t="n">
         <v>56000</v>
       </c>
-      <c r="O4" s="2" t="n">
+      <c r="O4" s="3" t="n">
         <v>9900</v>
       </c>
-      <c r="P4" s="2" t="n">
+      <c r="P4" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="Q4" s="2" t="n">
+      <c r="Q4" s="3" t="n">
         <v>1.25</v>
       </c>
-      <c r="R4" s="2" t="n">
+      <c r="R4" s="3" t="n">
         <v>1343</v>
       </c>
-      <c r="S4" s="2" t="n">
+      <c r="S4" s="3" t="n">
         <v>8000</v>
       </c>
-      <c r="T4" s="2" t="n">
+      <c r="T4" s="3" t="n">
         <v>1000</v>
       </c>
-      <c r="U4" s="2" t="n">
+      <c r="U4" s="3" t="n">
         <v>2444</v>
       </c>
-      <c r="V4" s="2" t="n">
+      <c r="V4" s="3" t="n">
         <v>28888</v>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="6">
+  <dataValidations count="5">
     <dataValidation allowBlank="false" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="F1:F998" type="list">
       <formula1>"Gold 14KT,Gold 18KT,Platinum"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="false" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D1:D3 D5:D998" type="list">
-      <formula1>"Bangles,Button,Cufflink,Pendant,Polki,Ring,Set,Tops,Chain,Bali,Tanmania,Mangalsutra"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="false" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="J1" type="none">
       <formula1>0</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="false" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="J2:J3 J5:J1004" type="list">
+    <dataValidation allowBlank="false" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="J238:J1004" type="list">
       <formula1>"Round,Radiant,Oval,Pear,Emerald,Rose Cut,Heart,Princess,Baguette,Cushion,Marquise"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="false" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="J4" type="list">
-      <formula1>"Round,Radiant,Oval,Pear,Emerald,Rose Cut,Heart,Princess,Baguette,Cushion,Marquise"</formula1>
+    <dataValidation allowBlank="false" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D1:D1004" type="list">
+      <formula1>"Bangles,Bracelet,Button,Cufflink,Pendant,Polki,Ring,Set,Tops,Chain,Bali,Tanmania,Mangalsutra"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="false" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D4" type="list">
-      <formula1>"Bangles,Bracelet,Button,Cufflink,Pendant,Polki,Ring,Set,Tops,Chain,Bali,Tanmania,Mangalsutra"</formula1>
+    <dataValidation allowBlank="false" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="J2:J237" type="list">
+      <formula1>"Round,Radiant,Oval,Pear,Pie Cut,Emerald,Rose Cut,Heart,Princess,Baguette,Cushion,Marquise"</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>

--- a/vgjewellry/public/sample/quotation_template_new.xlsx
+++ b/vgjewellry/public/sample/quotation_template_new.xlsx
@@ -254,9 +254,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>285120</xdr:colOff>
+      <xdr:colOff>284760</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>160560</xdr:rowOff>
+      <xdr:rowOff>160200</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -270,7 +270,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="1626840" y="450720"/>
-          <a:ext cx="285120" cy="160560"/>
+          <a:ext cx="284760" cy="160200"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -292,9 +292,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>285120</xdr:colOff>
+      <xdr:colOff>284760</xdr:colOff>
       <xdr:row>3</xdr:row>
-      <xdr:rowOff>160560</xdr:rowOff>
+      <xdr:rowOff>160200</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -308,7 +308,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="1626840" y="774720"/>
-          <a:ext cx="285120" cy="160560"/>
+          <a:ext cx="284760" cy="160200"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -658,7 +658,7 @@
       </c>
     </row>
   </sheetData>
-  <dataValidations count="5">
+  <dataValidations count="6">
     <dataValidation allowBlank="false" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="F1:F998" type="list">
       <formula1>"Gold 14KT,Gold 18KT,Platinum"</formula1>
       <formula2>0</formula2>
@@ -671,11 +671,15 @@
       <formula1>"Round,Radiant,Oval,Pear,Emerald,Rose Cut,Heart,Princess,Baguette,Cushion,Marquise"</formula1>
       <formula2>0</formula2>
     </dataValidation>
+    <dataValidation allowBlank="false" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="J163:J237" type="list">
+      <formula1>"Round,Radiant,Oval,Pear,Pie Cut,Emerald,Rose Cut,Heart,Princess,Baguette,Cushion,Marquise"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
     <dataValidation allowBlank="false" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D1:D1004" type="list">
       <formula1>"Bangles,Bracelet,Button,Cufflink,Pendant,Polki,Ring,Set,Tops,Chain,Bali,Tanmania,Mangalsutra"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="false" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="J2:J237" type="list">
+    <dataValidation allowBlank="false" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="J2:J162" type="list">
       <formula1>"Round,Radiant,Oval,Pear,Pie Cut,Emerald,Rose Cut,Heart,Princess,Baguette,Cushion,Marquise"</formula1>
       <formula2>0</formula2>
     </dataValidation>

--- a/vgjewellry/public/sample/quotation_template_new.xlsx
+++ b/vgjewellry/public/sample/quotation_template_new.xlsx
@@ -254,9 +254,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>284760</xdr:colOff>
+      <xdr:colOff>284400</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>160200</xdr:rowOff>
+      <xdr:rowOff>159840</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -270,7 +270,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="1626840" y="450720"/>
-          <a:ext cx="284760" cy="160200"/>
+          <a:ext cx="284400" cy="159840"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -292,9 +292,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>284760</xdr:colOff>
+      <xdr:colOff>284400</xdr:colOff>
       <xdr:row>3</xdr:row>
-      <xdr:rowOff>160200</xdr:rowOff>
+      <xdr:rowOff>159840</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -308,7 +308,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="1626840" y="774720"/>
-          <a:ext cx="284760" cy="160200"/>
+          <a:ext cx="284400" cy="159840"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -658,29 +658,17 @@
       </c>
     </row>
   </sheetData>
-  <dataValidations count="6">
+  <dataValidations count="3">
     <dataValidation allowBlank="false" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="F1:F998" type="list">
       <formula1>"Gold 14KT,Gold 18KT,Platinum"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="false" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="J1" type="none">
-      <formula1>0</formula1>
+    <dataValidation allowBlank="false" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D1:D1004" type="list">
+      <formula1>"Bali,Bangles,Bracelet,Button,Chain,Cufflink,Mangalsutra,Pendant,Polki,Ring,Set,Tanmania,Top"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="false" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="J238:J1004" type="list">
-      <formula1>"Round,Radiant,Oval,Pear,Emerald,Rose Cut,Heart,Princess,Baguette,Cushion,Marquise"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="false" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="J163:J237" type="list">
-      <formula1>"Round,Radiant,Oval,Pear,Pie Cut,Emerald,Rose Cut,Heart,Princess,Baguette,Cushion,Marquise"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="false" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D1:D1004" type="list">
-      <formula1>"Bangles,Bracelet,Button,Cufflink,Pendant,Polki,Ring,Set,Tops,Chain,Bali,Tanmania,Mangalsutra"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="false" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="J2:J162" type="list">
-      <formula1>"Round,Radiant,Oval,Pear,Pie Cut,Emerald,Rose Cut,Heart,Princess,Baguette,Cushion,Marquise"</formula1>
+    <dataValidation allowBlank="false" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="J1:J1004" type="list">
+      <formula1>"Baguette,Cushion,Emerald,Heart,Marquise,Oval,Pear,Pie Cut,Princess,Radiant,Rose Cut,Round"</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>

--- a/vgjewellry/public/sample/quotation_template_new.xlsx
+++ b/vgjewellry/public/sample/quotation_template_new.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
-  <fileVersion appName="Calc" lowestEdited="7"/>
+  <fileVersion appName="Calc"/>
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
@@ -254,9 +254,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>284400</xdr:colOff>
+      <xdr:colOff>283680</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>159840</xdr:rowOff>
+      <xdr:rowOff>159120</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -270,7 +270,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="1626840" y="450720"/>
-          <a:ext cx="284400" cy="159840"/>
+          <a:ext cx="283680" cy="159120"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -292,9 +292,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>284400</xdr:colOff>
+      <xdr:colOff>283680</xdr:colOff>
       <xdr:row>3</xdr:row>
-      <xdr:rowOff>159840</xdr:rowOff>
+      <xdr:rowOff>159120</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -307,8 +307,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1626840" y="774720"/>
-          <a:ext cx="284400" cy="159840"/>
+          <a:off x="1626840" y="949320"/>
+          <a:ext cx="283680" cy="159120"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -509,7 +509,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="26.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
         <v>22</v>
       </c>
@@ -595,7 +595,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="25.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3"/>
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
@@ -663,12 +663,12 @@
       <formula1>"Gold 14KT,Gold 18KT,Platinum"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="false" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D1:D1004" type="list">
-      <formula1>"Bali,Bangles,Bracelet,Button,Chain,Cufflink,Mangalsutra,Pendant,Polki,Ring,Set,Tanmania,Top"</formula1>
+    <dataValidation allowBlank="false" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="J1:J1004" type="list">
+      <formula1>"Baguette,Cushion,Emerald,Heart,Marquise,Oval,Pear,Pie Cut,Princess,Radiant,Rose Cut,Round"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="false" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="J1:J1004" type="list">
-      <formula1>"Baguette,Cushion,Emerald,Heart,Marquise,Oval,Pear,Pie Cut,Princess,Radiant,Rose Cut,Round"</formula1>
+    <dataValidation allowBlank="false" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D1:D1004" type="list">
+      <formula1>"Bali,Bangles,Bracelet,Button,Chain,Cufflink,Mangalsutra,Pendant,Polki,Ring,Set,Tanmania,Tops"</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
